--- a/bruno/testdata/servers_no_header.xlsx
+++ b/bruno/testdata/servers_no_header.xlsx
@@ -16,7 +16,7 @@
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
 <sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="3" uniqueCount="3">
   <si>
-    <t>server_name</t>
+    <t>Server Name</t>
   </si>
   <si>
     <t>some-server</t>
